--- a/DADES GENERALS.xlsx
+++ b/DADES GENERALS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Milanta\Documents\Arnau\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{053C6BB2-09A8-400D-AC02-F673C7BF8BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07BAF12-9FD6-40B8-8033-93D1C4F2F7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C268FE59-5D98-4779-93AE-6BAB9C17F435}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="31">
   <si>
     <t>Projecte</t>
   </si>
@@ -251,8 +251,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C6AB8C2D-6CAE-43E2-BFF7-DA0285178005}" name="Tabla1" displayName="Tabla1" ref="A1:J18" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:J18" xr:uid="{C6AB8C2D-6CAE-43E2-BFF7-DA0285178005}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C6AB8C2D-6CAE-43E2-BFF7-DA0285178005}" name="Tabla1" displayName="Tabla1" ref="A1:J22" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:J22" xr:uid="{C6AB8C2D-6CAE-43E2-BFF7-DA0285178005}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{6887BFB8-5A9B-4C98-AE4A-293DABAC48F6}" name="Projecte"/>
     <tableColumn id="2" xr3:uid="{C1A9F316-18D3-4A60-995E-0510E1E38994}" name="any" dataDxfId="8"/>
@@ -568,16 +568,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D38847F-D3AB-4048-9CC8-9BB16BDA546D}">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="4" max="5" width="13.44140625" customWidth="1"/>
     <col min="8" max="8" width="15.6640625" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="12" max="13" width="12.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -609,7 +610,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -643,7 +644,7 @@
       </c>
       <c r="K2" s="5"/>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -677,7 +678,7 @@
       </c>
       <c r="K3" s="5"/>
     </row>
-    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -710,8 +711,9 @@
         <v>205.12657575757578</v>
       </c>
       <c r="K4" s="5"/>
-    </row>
-    <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M4" s="5"/>
+    </row>
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -745,41 +747,42 @@
       </c>
       <c r="K5" s="5"/>
     </row>
-    <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B6" s="2">
         <v>2026</v>
       </c>
       <c r="C6" s="2">
-        <v>57</v>
+        <v>473</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I6" s="3">
-        <v>11467.91</v>
+        <v>104661.42</v>
       </c>
       <c r="J6" s="6">
         <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
-        <v>201.19140350877194</v>
+        <v>221.27150105708245</v>
       </c>
       <c r="K6" s="5"/>
-    </row>
-    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L6" s="5"/>
+    </row>
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -787,7 +790,7 @@
         <v>2026</v>
       </c>
       <c r="C7" s="2">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>4</v>
@@ -805,131 +808,132 @@
         <v>15</v>
       </c>
       <c r="I7" s="3">
+        <v>11467.91</v>
+      </c>
+      <c r="J7" s="6">
+        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <v>201.19140350877194</v>
+      </c>
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C8" s="2">
+        <v>80</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="3">
         <v>14830.645</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J8" s="6">
         <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
         <v>185.38306249999999</v>
       </c>
-      <c r="K7" s="5"/>
-    </row>
-    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C9" s="2">
+        <v>137</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="3">
+        <v>26298.560000000001</v>
+      </c>
+      <c r="J9" s="6">
+        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <v>191.96029197080293</v>
+      </c>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+    </row>
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="2">
-        <v>2026</v>
-      </c>
-      <c r="C8" s="4">
+      <c r="B10" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C10" s="4">
         <v>127</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I10" s="3">
         <v>14505.78</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J10" s="6">
         <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
         <v>114.21874015748033</v>
       </c>
-      <c r="K8" s="5"/>
-    </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="2">
-        <v>2026</v>
-      </c>
-      <c r="C9" s="2">
+      <c r="B11" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C11" s="2">
         <v>270</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="3">
-        <v>33376.310000000005</v>
-      </c>
-      <c r="J9" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
-        <v>123.61596296296298</v>
-      </c>
-      <c r="K9" s="5"/>
-    </row>
-    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="2">
-        <v>2026</v>
-      </c>
-      <c r="C10" s="2">
-        <v>233</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="3">
-        <v>40505.639999999992</v>
-      </c>
-      <c r="J10" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
-        <v>173.84394849785406</v>
-      </c>
-      <c r="K10" s="5"/>
-    </row>
-    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="2">
-        <v>2026</v>
-      </c>
-      <c r="C11" s="2">
-        <v>84</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>6</v>
@@ -941,49 +945,49 @@
         <v>14</v>
       </c>
       <c r="I11" s="3">
-        <v>21659.300000000003</v>
+        <v>33376.310000000005</v>
       </c>
       <c r="J11" s="6">
         <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
-        <v>257.84880952380956</v>
+        <v>123.61596296296298</v>
       </c>
       <c r="K11" s="5"/>
     </row>
-    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2">
         <v>2026</v>
       </c>
       <c r="C12" s="2">
-        <v>107</v>
+        <v>233</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I12" s="3">
-        <v>15683.06</v>
+        <v>40505.639999999992</v>
       </c>
       <c r="J12" s="6">
         <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
-        <v>146.57065420560747</v>
+        <v>173.84394849785406</v>
       </c>
       <c r="K12" s="5"/>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -991,149 +995,151 @@
         <v>2026</v>
       </c>
       <c r="C13" s="2">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="3">
+        <v>21659.300000000003</v>
+      </c>
+      <c r="J13" s="6">
+        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <v>257.84880952380956</v>
+      </c>
+      <c r="K13" s="5"/>
+    </row>
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C14" s="2">
+        <v>107</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I13" s="3">
-        <v>19598.924999999999</v>
-      </c>
-      <c r="J13" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
-        <v>199.9890306122449</v>
-      </c>
-      <c r="K13" s="5"/>
-    </row>
-    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="2">
-        <v>2026</v>
-      </c>
-      <c r="C14" s="2">
-        <v>160</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="F14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I14" s="3">
-        <v>56245.774999999994</v>
+        <v>15683.06</v>
       </c>
       <c r="J14" s="6">
         <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
-        <v>351.53609374999996</v>
+        <v>146.57065420560747</v>
       </c>
       <c r="K14" s="5"/>
     </row>
-    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="2">
         <v>2026</v>
       </c>
       <c r="C15" s="2">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>27</v>
       </c>
       <c r="I15" s="3">
-        <v>36517.54</v>
+        <v>19598.924999999999</v>
       </c>
       <c r="J15" s="6">
         <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
-        <v>429.61811764705885</v>
+        <v>199.9890306122449</v>
       </c>
       <c r="K15" s="5"/>
-    </row>
-    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M15" s="5"/>
+    </row>
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C16" s="2">
+        <v>289</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="3">
+        <v>56941.29</v>
+      </c>
+      <c r="J16" s="6">
+        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <v>197.02868512110726</v>
+      </c>
+      <c r="K16" s="5"/>
+      <c r="M16" s="5"/>
+    </row>
+    <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="2">
-        <v>2026</v>
-      </c>
-      <c r="C16" s="2">
-        <v>92</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I16" s="3">
-        <v>25838.73</v>
-      </c>
-      <c r="J16" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
-        <v>280.85576086956519</v>
-      </c>
-      <c r="K16" s="5"/>
-    </row>
-    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>25</v>
-      </c>
       <c r="B17" s="2">
         <v>2026</v>
       </c>
       <c r="C17" s="2">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>6</v>
@@ -1142,90 +1148,228 @@
         <v>28</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="3">
+        <v>56245.774999999994</v>
+      </c>
+      <c r="J17" s="6">
+        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <v>351.53609374999996</v>
+      </c>
+      <c r="K17" s="5"/>
+    </row>
+    <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C18" s="2">
+        <v>85</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I18" s="3">
+        <v>36517.54</v>
+      </c>
+      <c r="J18" s="6">
+        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <v>429.61811764705885</v>
+      </c>
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C19" s="2">
+        <v>92</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I19" s="3">
+        <v>25838.73</v>
+      </c>
+      <c r="J19" s="6">
+        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <v>280.85576086956519</v>
+      </c>
+      <c r="K19" s="5"/>
+      <c r="M19" s="5"/>
+    </row>
+    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C20" s="2">
+        <v>337</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I20" s="3">
+        <v>118602.05</v>
+      </c>
+      <c r="J20" s="6">
+        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <v>351.93486646884276</v>
+      </c>
+      <c r="K20" s="5"/>
+      <c r="M20" s="5"/>
+    </row>
+    <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C21" s="2">
+        <v>148</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="3">
         <v>44771.630000000005</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J21" s="6">
         <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
         <v>302.51101351351355</v>
       </c>
-      <c r="K17" s="5"/>
-    </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="2">
-        <v>2026</v>
-      </c>
-      <c r="C18" s="2">
+      <c r="B22" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C22" s="2">
         <v>172</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I22" s="3">
         <v>39267.870000000003</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J22" s="6">
         <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
         <v>228.30156976744186</v>
       </c>
-      <c r="K18" s="5"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
+      <c r="K22" s="5"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DADES GENERALS.xlsx
+++ b/DADES GENERALS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Milanta\Documents\Arnau\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07BAF12-9FD6-40B8-8033-93D1C4F2F7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55247CDC-D02E-4113-BF21-8D28F1B711CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C268FE59-5D98-4779-93AE-6BAB9C17F435}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="33">
   <si>
     <t>Projecte</t>
   </si>
@@ -63,9 +63,6 @@
     <t>tipologia</t>
   </si>
   <si>
-    <t>preu total</t>
-  </si>
-  <si>
     <t>espai trobada</t>
   </si>
   <si>
@@ -123,10 +120,19 @@
     <t>parcial</t>
   </si>
   <si>
-    <t>preu/m²</t>
-  </si>
-  <si>
     <t>maquina</t>
+  </si>
+  <si>
+    <t>P.T.</t>
+  </si>
+  <si>
+    <t>P.T./m²</t>
+  </si>
+  <si>
+    <t>P.Net</t>
+  </si>
+  <si>
+    <t>P.Net/m²</t>
   </si>
 </sst>
 </file>
@@ -202,7 +208,14 @@
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="13">
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -251,20 +264,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C6AB8C2D-6CAE-43E2-BFF7-DA0285178005}" name="Tabla1" displayName="Tabla1" ref="A1:J22" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:J22" xr:uid="{C6AB8C2D-6CAE-43E2-BFF7-DA0285178005}"/>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C6AB8C2D-6CAE-43E2-BFF7-DA0285178005}" name="Tabla1" displayName="Tabla1" ref="A1:L22" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:L22" xr:uid="{C6AB8C2D-6CAE-43E2-BFF7-DA0285178005}"/>
+  <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{6887BFB8-5A9B-4C98-AE4A-293DABAC48F6}" name="Projecte"/>
-    <tableColumn id="2" xr3:uid="{C1A9F316-18D3-4A60-995E-0510E1E38994}" name="any" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{A49F3AC1-2DB8-49BD-8AE8-D7A6BD53FD1C}" name="m²" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{6360ECFB-ACB8-4EE0-8AA6-420E84005DCC}" name="accessibilitat" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{8F8819C9-807F-411A-93DF-7A62851E0DE1}" name="complexitat" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{0FA0DEE6-319E-4E28-8639-D1AC765324AA}" name="maquina" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{D429A092-929E-4492-AE35-031BDFCECC30}" name="repicat" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{B58ED1BD-BB0A-4CB1-83E2-15AFF59C3B36}" name="tipologia" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{E4306E95-4489-41CD-8C53-515FB4249D41}" name="preu total" dataDxfId="1" dataCellStyle="Moneda"/>
-    <tableColumn id="7" xr3:uid="{8DA87BDA-9696-4A6B-AFF2-C3896906BAE5}" name="preu/m²" dataDxfId="0">
-      <calculatedColumnFormula>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{C1A9F316-18D3-4A60-995E-0510E1E38994}" name="any" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{A49F3AC1-2DB8-49BD-8AE8-D7A6BD53FD1C}" name="m²" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{6360ECFB-ACB8-4EE0-8AA6-420E84005DCC}" name="accessibilitat" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{8F8819C9-807F-411A-93DF-7A62851E0DE1}" name="complexitat" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{0FA0DEE6-319E-4E28-8639-D1AC765324AA}" name="maquina" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{D429A092-929E-4492-AE35-031BDFCECC30}" name="repicat" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{B58ED1BD-BB0A-4CB1-83E2-15AFF59C3B36}" name="tipologia" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{E4306E95-4489-41CD-8C53-515FB4249D41}" name="P.T." dataDxfId="3" dataCellStyle="Moneda"/>
+    <tableColumn id="7" xr3:uid="{8DA87BDA-9696-4A6B-AFF2-C3896906BAE5}" name="P.T./m²" dataDxfId="2">
+      <calculatedColumnFormula>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{58AE9255-0D1B-41E3-984E-702530FBD4F9}" name="P.Net" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{0DDD4FF3-6428-4E50-B3B9-B57AD4819EA0}" name="P.Net/m²" dataDxfId="0">
+      <calculatedColumnFormula>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -575,7 +592,7 @@
     <col min="4" max="5" width="13.44140625" customWidth="1"/>
     <col min="8" max="8" width="15.6640625" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="12" max="13" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="12.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -592,10 +609,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -604,10 +621,16 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -624,25 +647,31 @@
         <v>4</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I2" s="3">
         <v>11914.6</v>
       </c>
       <c r="J2" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
         <v>248.22083333333333</v>
       </c>
-      <c r="K2" s="5"/>
+      <c r="K2" s="6">
+        <v>10384.6</v>
+      </c>
+      <c r="L2" s="6">
+        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>216.34583333333333</v>
+      </c>
     </row>
     <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -658,25 +687,31 @@
         <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I3" s="3">
         <v>39228.730000000003</v>
       </c>
       <c r="J3" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
         <v>186.8034761904762</v>
       </c>
-      <c r="K3" s="5"/>
+      <c r="K3" s="6">
+        <v>34710.730000000003</v>
+      </c>
+      <c r="L3" s="6">
+        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>165.2891904761905</v>
+      </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -692,25 +727,31 @@
         <v>4</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I4" s="3">
         <v>33845.885000000002</v>
       </c>
       <c r="J4" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
         <v>205.12657575757578</v>
       </c>
-      <c r="K4" s="5"/>
+      <c r="K4" s="6">
+        <v>31143.89</v>
+      </c>
+      <c r="L4" s="6">
+        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>188.75084848484849</v>
+      </c>
       <c r="M4" s="5"/>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -727,25 +768,31 @@
         <v>4</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I5" s="3">
         <v>19672.2</v>
       </c>
       <c r="J5" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
         <v>393.44400000000002</v>
       </c>
-      <c r="K5" s="5"/>
+      <c r="K5" s="6">
+        <v>18562</v>
+      </c>
+      <c r="L5" s="6">
+        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>371.24</v>
+      </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -761,30 +808,35 @@
         <v>4</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I6" s="3">
         <v>104661.42</v>
       </c>
       <c r="J6" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
         <v>221.27150105708245</v>
       </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
+      <c r="K6" s="6">
+        <v>94801.22</v>
+      </c>
+      <c r="L6" s="6">
+        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>200.42541226215644</v>
+      </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2">
         <v>2026</v>
@@ -796,29 +848,35 @@
         <v>4</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="G7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I7" s="3">
         <v>11467.91</v>
       </c>
       <c r="J7" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
         <v>201.19140350877194</v>
       </c>
-      <c r="K7" s="5"/>
+      <c r="K7" s="6">
+        <v>11467.91</v>
+      </c>
+      <c r="L7" s="6">
+        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>201.19140350877194</v>
+      </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="2">
         <v>2026</v>
@@ -830,29 +888,35 @@
         <v>4</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="G8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I8" s="3">
         <v>14830.645</v>
       </c>
       <c r="J8" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
         <v>185.38306249999999</v>
       </c>
-      <c r="K8" s="5"/>
+      <c r="K8" s="6">
+        <v>14830.65</v>
+      </c>
+      <c r="L8" s="6">
+        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>185.38312500000001</v>
+      </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="2">
         <v>2026</v>
@@ -864,30 +928,35 @@
         <v>4</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I9" s="3">
         <v>26298.560000000001</v>
       </c>
       <c r="J9" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
         <v>191.96029197080293</v>
       </c>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
+      <c r="K9" s="6">
+        <v>26298.560000000001</v>
+      </c>
+      <c r="L9" s="6">
+        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>191.96029197080293</v>
+      </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2">
         <v>2026</v>
@@ -899,29 +968,35 @@
         <v>4</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I10" s="3">
         <v>14505.78</v>
       </c>
       <c r="J10" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
         <v>114.21874015748033</v>
       </c>
-      <c r="K10" s="5"/>
+      <c r="K10" s="6">
+        <v>14505.78</v>
+      </c>
+      <c r="L10" s="6">
+        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>114.21874015748033</v>
+      </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="2">
         <v>2026</v>
@@ -930,32 +1005,38 @@
         <v>270</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I11" s="3">
         <v>33376.310000000005</v>
       </c>
       <c r="J11" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
         <v>123.61596296296298</v>
       </c>
-      <c r="K11" s="5"/>
+      <c r="K11" s="6">
+        <v>31776.31</v>
+      </c>
+      <c r="L11" s="6">
+        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>117.69003703703704</v>
+      </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" s="2">
         <v>2026</v>
@@ -964,32 +1045,38 @@
         <v>233</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="I12" s="3">
         <v>40505.639999999992</v>
       </c>
       <c r="J12" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
         <v>173.84394849785406</v>
       </c>
-      <c r="K12" s="5"/>
+      <c r="K12" s="6">
+        <v>36661.64</v>
+      </c>
+      <c r="L12" s="6">
+        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>157.34609442060085</v>
+      </c>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2">
         <v>2026</v>
@@ -1001,29 +1088,35 @@
         <v>4</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I13" s="3">
         <v>21659.300000000003</v>
       </c>
       <c r="J13" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
         <v>257.84880952380956</v>
       </c>
-      <c r="K13" s="5"/>
+      <c r="K13" s="6">
+        <v>19859.3</v>
+      </c>
+      <c r="L13" s="6">
+        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>236.42023809523809</v>
+      </c>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="2">
         <v>2026</v>
@@ -1035,29 +1128,35 @@
         <v>4</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I14" s="3">
         <v>15683.06</v>
       </c>
       <c r="J14" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
         <v>146.57065420560747</v>
       </c>
-      <c r="K14" s="5"/>
+      <c r="K14" s="6">
+        <v>14298.06</v>
+      </c>
+      <c r="L14" s="6">
+        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>133.62672897196262</v>
+      </c>
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="2">
         <v>2026</v>
@@ -1069,30 +1168,36 @@
         <v>4</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I15" s="3">
         <v>19598.924999999999</v>
       </c>
       <c r="J15" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
         <v>199.9890306122449</v>
       </c>
-      <c r="K15" s="5"/>
+      <c r="K15" s="6">
+        <v>17989.93</v>
+      </c>
+      <c r="L15" s="6">
+        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>183.5707142857143</v>
+      </c>
       <c r="M15" s="5"/>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="2">
         <v>2026</v>
@@ -1104,30 +1209,36 @@
         <v>4</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I16" s="3">
         <v>56941.29</v>
       </c>
       <c r="J16" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
         <v>197.02868512110726</v>
       </c>
-      <c r="K16" s="5"/>
+      <c r="K16" s="6">
+        <v>52147.29</v>
+      </c>
+      <c r="L16" s="6">
+        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>180.44044982698964</v>
+      </c>
       <c r="M16" s="5"/>
     </row>
     <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="2">
         <v>2026</v>
@@ -1139,29 +1250,35 @@
         <v>4</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I17" s="3">
         <v>56245.774999999994</v>
       </c>
       <c r="J17" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
         <v>351.53609374999996</v>
       </c>
-      <c r="K17" s="5"/>
+      <c r="K17" s="6">
+        <v>53195.78</v>
+      </c>
+      <c r="L17" s="6">
+        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>332.47362499999997</v>
+      </c>
     </row>
     <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" s="2">
         <v>2026</v>
@@ -1173,29 +1290,35 @@
         <v>4</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I18" s="3">
         <v>36517.54</v>
       </c>
       <c r="J18" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
         <v>429.61811764705885</v>
       </c>
-      <c r="K18" s="5"/>
+      <c r="K18" s="6">
+        <v>33577.54</v>
+      </c>
+      <c r="L18" s="6">
+        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>395.02988235294117</v>
+      </c>
     </row>
     <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" s="2">
         <v>2026</v>
@@ -1207,30 +1330,36 @@
         <v>4</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I19" s="3">
         <v>25838.73</v>
       </c>
       <c r="J19" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
         <v>280.85576086956519</v>
       </c>
-      <c r="K19" s="5"/>
+      <c r="K19" s="6">
+        <v>22239.73</v>
+      </c>
+      <c r="L19" s="6">
+        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>241.7361956521739</v>
+      </c>
       <c r="M19" s="5"/>
     </row>
     <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" s="2">
         <v>2026</v>
@@ -1242,30 +1371,36 @@
         <v>4</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I20" s="3">
         <v>118602.05</v>
       </c>
       <c r="J20" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
         <v>351.93486646884276</v>
       </c>
-      <c r="K20" s="5"/>
+      <c r="K20" s="6">
+        <v>109012.05</v>
+      </c>
+      <c r="L20" s="6">
+        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>323.4778931750742</v>
+      </c>
       <c r="M20" s="5"/>
     </row>
     <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B21" s="2">
         <v>2026</v>
@@ -1274,32 +1409,38 @@
         <v>148</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I21" s="3">
         <v>44771.630000000005</v>
       </c>
       <c r="J21" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
         <v>302.51101351351355</v>
       </c>
-      <c r="K21" s="5"/>
+      <c r="K21" s="6">
+        <v>37491.629999999997</v>
+      </c>
+      <c r="L21" s="6">
+        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>253.3218243243243</v>
+      </c>
     </row>
     <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" s="2">
         <v>2026</v>
@@ -1308,28 +1449,34 @@
         <v>172</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I22" s="3">
         <v>39267.870000000003</v>
       </c>
       <c r="J22" s="6">
-        <f>Tabla1[[#This Row],[preu total]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
         <v>228.30156976744186</v>
       </c>
-      <c r="K22" s="5"/>
+      <c r="K22" s="6">
+        <v>35117.879999999997</v>
+      </c>
+      <c r="L22" s="6">
+        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>204.17372093023255</v>
+      </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B23" s="2"/>

--- a/DADES GENERALS.xlsx
+++ b/DADES GENERALS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Milanta\Documents\Arnau\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55247CDC-D02E-4113-BF21-8D28F1B711CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5558B491-9D37-44A1-9D77-D9C05EB7D2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C268FE59-5D98-4779-93AE-6BAB9C17F435}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="34">
   <si>
     <t>Projecte</t>
   </si>
@@ -123,16 +123,19 @@
     <t>maquina</t>
   </si>
   <si>
-    <t>P.T.</t>
-  </si>
-  <si>
-    <t>P.T./m²</t>
-  </si>
-  <si>
-    <t>P.Net</t>
-  </si>
-  <si>
-    <t>P.Net/m²</t>
+    <t>Baldufa - Quart</t>
+  </si>
+  <si>
+    <t>p.t./m²</t>
+  </si>
+  <si>
+    <t>p.t.</t>
+  </si>
+  <si>
+    <t>p.net</t>
+  </si>
+  <si>
+    <t>p.net/m²</t>
   </si>
 </sst>
 </file>
@@ -264,8 +267,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C6AB8C2D-6CAE-43E2-BFF7-DA0285178005}" name="Tabla1" displayName="Tabla1" ref="A1:L22" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:L22" xr:uid="{C6AB8C2D-6CAE-43E2-BFF7-DA0285178005}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C6AB8C2D-6CAE-43E2-BFF7-DA0285178005}" name="Tabla1" displayName="Tabla1" ref="A1:L19" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:L19" xr:uid="{C6AB8C2D-6CAE-43E2-BFF7-DA0285178005}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{6887BFB8-5A9B-4C98-AE4A-293DABAC48F6}" name="Projecte"/>
     <tableColumn id="2" xr3:uid="{C1A9F316-18D3-4A60-995E-0510E1E38994}" name="any" dataDxfId="10"/>
@@ -275,13 +278,13 @@
     <tableColumn id="5" xr3:uid="{0FA0DEE6-319E-4E28-8639-D1AC765324AA}" name="maquina" dataDxfId="6"/>
     <tableColumn id="6" xr3:uid="{D429A092-929E-4492-AE35-031BDFCECC30}" name="repicat" dataDxfId="5"/>
     <tableColumn id="8" xr3:uid="{B58ED1BD-BB0A-4CB1-83E2-15AFF59C3B36}" name="tipologia" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{E4306E95-4489-41CD-8C53-515FB4249D41}" name="P.T." dataDxfId="3" dataCellStyle="Moneda"/>
-    <tableColumn id="7" xr3:uid="{8DA87BDA-9696-4A6B-AFF2-C3896906BAE5}" name="P.T./m²" dataDxfId="2">
-      <calculatedColumnFormula>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</calculatedColumnFormula>
+    <tableColumn id="9" xr3:uid="{E4306E95-4489-41CD-8C53-515FB4249D41}" name="p.t." dataDxfId="3" dataCellStyle="Moneda"/>
+    <tableColumn id="7" xr3:uid="{8DA87BDA-9696-4A6B-AFF2-C3896906BAE5}" name="p.t./m²" dataDxfId="2">
+      <calculatedColumnFormula>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{58AE9255-0D1B-41E3-984E-702530FBD4F9}" name="P.Net" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{0DDD4FF3-6428-4E50-B3B9-B57AD4819EA0}" name="P.Net/m²" dataDxfId="0">
-      <calculatedColumnFormula>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</calculatedColumnFormula>
+    <tableColumn id="11" xr3:uid="{58AE9255-0D1B-41E3-984E-702530FBD4F9}" name="p.net" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{0DDD4FF3-6428-4E50-B3B9-B57AD4819EA0}" name="p.net/m²" dataDxfId="0">
+      <calculatedColumnFormula>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -585,7 +588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D38847F-D3AB-4048-9CC8-9BB16BDA546D}">
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -621,16 +624,16 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -662,14 +665,14 @@
         <v>11914.6</v>
       </c>
       <c r="J2" s="6">
-        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
         <v>248.22083333333333</v>
       </c>
       <c r="K2" s="6">
         <v>10384.6</v>
       </c>
       <c r="L2" s="6">
-        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
         <v>216.34583333333333</v>
       </c>
     </row>
@@ -702,14 +705,14 @@
         <v>39228.730000000003</v>
       </c>
       <c r="J3" s="6">
-        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
         <v>186.8034761904762</v>
       </c>
       <c r="K3" s="6">
         <v>34710.730000000003</v>
       </c>
       <c r="L3" s="6">
-        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
         <v>165.2891904761905</v>
       </c>
     </row>
@@ -742,14 +745,14 @@
         <v>33845.885000000002</v>
       </c>
       <c r="J4" s="6">
-        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
         <v>205.12657575757578</v>
       </c>
       <c r="K4" s="6">
         <v>31143.89</v>
       </c>
       <c r="L4" s="6">
-        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
         <v>188.75084848484849</v>
       </c>
       <c r="M4" s="5"/>
@@ -783,55 +786,55 @@
         <v>19672.2</v>
       </c>
       <c r="J5" s="6">
-        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
         <v>393.44400000000002</v>
       </c>
       <c r="K5" s="6">
         <v>18562</v>
       </c>
       <c r="L5" s="6">
-        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
+        <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
         <v>371.24</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2">
         <v>2026</v>
       </c>
       <c r="C6" s="2">
-        <v>473</v>
+        <v>57</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6" s="3">
-        <v>104661.42</v>
+        <v>11467.91</v>
       </c>
       <c r="J6" s="6">
-        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
-        <v>221.27150105708245</v>
+        <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
+        <v>201.19140350877194</v>
       </c>
       <c r="K6" s="6">
-        <v>94801.22</v>
+        <v>11467.91</v>
       </c>
       <c r="L6" s="6">
-        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
-        <v>200.42541226215644</v>
+        <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>201.19140350877194</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -842,7 +845,7 @@
         <v>2026</v>
       </c>
       <c r="C7" s="2">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>4</v>
@@ -860,35 +863,35 @@
         <v>14</v>
       </c>
       <c r="I7" s="3">
-        <v>11467.91</v>
+        <v>14830.645</v>
       </c>
       <c r="J7" s="6">
-        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
-        <v>201.19140350877194</v>
+        <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
+        <v>185.38306249999999</v>
       </c>
       <c r="K7" s="6">
-        <v>11467.91</v>
+        <v>14830.65</v>
       </c>
       <c r="L7" s="6">
-        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
-        <v>201.19140350877194</v>
+        <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>185.38312500000001</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2">
         <v>2026</v>
       </c>
-      <c r="C8" s="2">
-        <v>80</v>
+      <c r="C8" s="4">
+        <v>127</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>16</v>
@@ -897,118 +900,118 @@
         <v>16</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I8" s="3">
-        <v>14830.645</v>
+        <v>14505.78</v>
       </c>
       <c r="J8" s="6">
-        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
-        <v>185.38306249999999</v>
+        <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
+        <v>114.21874015748033</v>
       </c>
       <c r="K8" s="6">
-        <v>14830.65</v>
+        <v>14505.78</v>
       </c>
       <c r="L8" s="6">
-        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
-        <v>185.38312500000001</v>
+        <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>114.21874015748033</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2">
         <v>2026</v>
       </c>
       <c r="C9" s="2">
-        <v>137</v>
+        <v>270</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I9" s="3">
-        <v>26298.560000000001</v>
+        <v>33376.310000000005</v>
       </c>
       <c r="J9" s="6">
-        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
-        <v>191.96029197080293</v>
+        <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
+        <v>123.61596296296298</v>
       </c>
       <c r="K9" s="6">
-        <v>26298.560000000001</v>
+        <v>31776.31</v>
       </c>
       <c r="L9" s="6">
-        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
-        <v>191.96029197080293</v>
+        <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>117.69003703703704</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B10" s="2">
         <v>2026</v>
       </c>
-      <c r="C10" s="4">
-        <v>127</v>
+      <c r="C10" s="2">
+        <v>233</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I10" s="3">
-        <v>14505.78</v>
+        <v>40505.639999999992</v>
       </c>
       <c r="J10" s="6">
-        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
-        <v>114.21874015748033</v>
+        <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
+        <v>173.84394849785406</v>
       </c>
       <c r="K10" s="6">
-        <v>14505.78</v>
+        <v>36661.64</v>
       </c>
       <c r="L10" s="6">
-        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
-        <v>114.21874015748033</v>
+        <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>157.34609442060085</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2">
         <v>2026</v>
       </c>
       <c r="C11" s="2">
-        <v>270</v>
+        <v>91</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>6</v>
@@ -1020,58 +1023,58 @@
         <v>13</v>
       </c>
       <c r="I11" s="3">
-        <v>33376.310000000005</v>
+        <v>21659.300000000003</v>
       </c>
       <c r="J11" s="6">
-        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
-        <v>123.61596296296298</v>
+        <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
+        <v>238.01428571428573</v>
       </c>
       <c r="K11" s="6">
-        <v>31776.31</v>
+        <v>19859.3</v>
       </c>
       <c r="L11" s="6">
-        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
-        <v>117.69003703703704</v>
+        <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>218.23406593406594</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2">
         <v>2026</v>
       </c>
       <c r="C12" s="2">
-        <v>233</v>
+        <v>107</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="H12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="3">
-        <v>40505.639999999992</v>
+        <v>15683.06</v>
       </c>
       <c r="J12" s="6">
-        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
-        <v>173.84394849785406</v>
+        <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
+        <v>146.57065420560747</v>
       </c>
       <c r="K12" s="6">
-        <v>36661.64</v>
+        <v>14298.06</v>
       </c>
       <c r="L12" s="6">
-        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
-        <v>157.34609442060085</v>
+        <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>133.62672897196262</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1082,13 +1085,13 @@
         <v>2026</v>
       </c>
       <c r="C13" s="2">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>6</v>
@@ -1097,160 +1100,160 @@
         <v>16</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="I13" s="3">
-        <v>21659.300000000003</v>
+        <v>19598.924999999999</v>
       </c>
       <c r="J13" s="6">
-        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
-        <v>257.84880952380956</v>
+        <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
+        <v>199.9890306122449</v>
       </c>
       <c r="K13" s="6">
-        <v>19859.3</v>
+        <v>17989.93</v>
       </c>
       <c r="L13" s="6">
-        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
-        <v>236.42023809523809</v>
-      </c>
+        <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>183.5707142857143</v>
+      </c>
+      <c r="M13" s="5"/>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2">
         <v>2026</v>
       </c>
       <c r="C14" s="2">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I14" s="3">
-        <v>15683.06</v>
+        <v>56245.774999999994</v>
       </c>
       <c r="J14" s="6">
-        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
-        <v>146.57065420560747</v>
+        <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
+        <v>351.53609374999996</v>
       </c>
       <c r="K14" s="6">
-        <v>14298.06</v>
+        <v>53195.78</v>
       </c>
       <c r="L14" s="6">
-        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
-        <v>133.62672897196262</v>
+        <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>332.47362499999997</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="2">
         <v>2026</v>
       </c>
       <c r="C15" s="2">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>26</v>
       </c>
       <c r="I15" s="3">
-        <v>19598.924999999999</v>
+        <v>36517.54</v>
       </c>
       <c r="J15" s="6">
-        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
-        <v>199.9890306122449</v>
+        <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
+        <v>429.61811764705885</v>
       </c>
       <c r="K15" s="6">
-        <v>17989.93</v>
+        <v>33577.54</v>
       </c>
       <c r="L15" s="6">
-        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
-        <v>183.5707142857143</v>
-      </c>
-      <c r="M15" s="5"/>
+        <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>395.02988235294117</v>
+      </c>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="2">
         <v>2026</v>
       </c>
       <c r="C16" s="2">
-        <v>289</v>
+        <v>92</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I16" s="3">
-        <v>56941.29</v>
+        <v>25838.73</v>
       </c>
       <c r="J16" s="6">
-        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
-        <v>197.02868512110726</v>
+        <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
+        <v>280.85576086956519</v>
       </c>
       <c r="K16" s="6">
-        <v>52147.29</v>
+        <v>22239.73</v>
       </c>
       <c r="L16" s="6">
-        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
-        <v>180.44044982698964</v>
+        <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>241.7361956521739</v>
       </c>
       <c r="M16" s="5"/>
     </row>
-    <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="2">
         <v>2026</v>
       </c>
       <c r="C17" s="2">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>6</v>
@@ -1259,264 +1262,112 @@
         <v>27</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I17" s="3">
-        <v>56245.774999999994</v>
+        <v>44771.630000000005</v>
       </c>
       <c r="J17" s="6">
-        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
-        <v>351.53609374999996</v>
+        <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
+        <v>302.51101351351355</v>
       </c>
       <c r="K17" s="6">
-        <v>53195.78</v>
+        <v>37491.629999999997</v>
       </c>
       <c r="L17" s="6">
-        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
-        <v>332.47362499999997</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>253.3218243243243</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B18" s="2">
         <v>2026</v>
       </c>
       <c r="C18" s="2">
-        <v>85</v>
+        <v>172</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="I18" s="3">
-        <v>36517.54</v>
+        <v>39267.870000000003</v>
       </c>
       <c r="J18" s="6">
-        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
-        <v>429.61811764705885</v>
+        <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
+        <v>228.30156976744186</v>
       </c>
       <c r="K18" s="6">
-        <v>33577.54</v>
+        <v>35117.879999999997</v>
       </c>
       <c r="L18" s="6">
-        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
-        <v>395.02988235294117</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>204.17372093023255</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B19" s="2">
         <v>2026</v>
       </c>
       <c r="C19" s="2">
-        <v>92</v>
+        <v>210</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I19" s="3">
-        <v>25838.73</v>
+        <v>36053.57</v>
       </c>
       <c r="J19" s="6">
-        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
-        <v>280.85576086956519</v>
-      </c>
-      <c r="K19" s="6">
-        <v>22239.73</v>
+        <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
+        <v>171.68366666666665</v>
+      </c>
+      <c r="K19" s="3">
+        <v>36053.57</v>
       </c>
       <c r="L19" s="6">
-        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
-        <v>241.7361956521739</v>
-      </c>
-      <c r="M19" s="5"/>
-    </row>
-    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="2">
-        <v>2026</v>
-      </c>
-      <c r="C20" s="2">
-        <v>337</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="3">
-        <v>118602.05</v>
-      </c>
-      <c r="J20" s="6">
-        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
-        <v>351.93486646884276</v>
-      </c>
-      <c r="K20" s="6">
-        <v>109012.05</v>
-      </c>
-      <c r="L20" s="6">
-        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
-        <v>323.4778931750742</v>
-      </c>
-      <c r="M20" s="5"/>
-    </row>
-    <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="2">
-        <v>2026</v>
-      </c>
-      <c r="C21" s="2">
-        <v>148</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="3">
-        <v>44771.630000000005</v>
-      </c>
-      <c r="J21" s="6">
-        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
-        <v>302.51101351351355</v>
-      </c>
-      <c r="K21" s="6">
-        <v>37491.629999999997</v>
-      </c>
-      <c r="L21" s="6">
-        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
-        <v>253.3218243243243</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="2">
-        <v>2026</v>
-      </c>
-      <c r="C22" s="2">
-        <v>172</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" s="3">
-        <v>39267.870000000003</v>
-      </c>
-      <c r="J22" s="6">
-        <f>Tabla1[[#This Row],[P.T.]]/Tabla1[[#This Row],[m²]]</f>
-        <v>228.30156976744186</v>
-      </c>
-      <c r="K22" s="6">
-        <v>35117.879999999997</v>
-      </c>
-      <c r="L22" s="6">
-        <f>Tabla1[[#This Row],[P.Net]]/Tabla1[[#This Row],[m²]]</f>
-        <v>204.17372093023255</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
+        <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>171.68366666666665</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DADES GENERALS.xlsx
+++ b/DADES GENERALS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Milanta\Documents\Arnau\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5558B491-9D37-44A1-9D77-D9C05EB7D2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC2F9A9B-6AF3-478C-929D-BBCE59FA40E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C268FE59-5D98-4779-93AE-6BAB9C17F435}"/>
+    <workbookView xWindow="1008" yWindow="96" windowWidth="15288" windowHeight="12240" xr2:uid="{C268FE59-5D98-4779-93AE-6BAB9C17F435}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="37">
   <si>
     <t>Projecte</t>
   </si>
@@ -136,6 +136,15 @@
   </si>
   <si>
     <t>p.net/m²</t>
+  </si>
+  <si>
+    <t>La Salle - Reus</t>
+  </si>
+  <si>
+    <t>Sa Sitra - Porreres</t>
+  </si>
+  <si>
+    <t>total</t>
   </si>
 </sst>
 </file>
@@ -267,8 +276,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C6AB8C2D-6CAE-43E2-BFF7-DA0285178005}" name="Tabla1" displayName="Tabla1" ref="A1:L19" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:L19" xr:uid="{C6AB8C2D-6CAE-43E2-BFF7-DA0285178005}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C6AB8C2D-6CAE-43E2-BFF7-DA0285178005}" name="Tabla1" displayName="Tabla1" ref="A1:L22" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:L22" xr:uid="{C6AB8C2D-6CAE-43E2-BFF7-DA0285178005}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{6887BFB8-5A9B-4C98-AE4A-293DABAC48F6}" name="Projecte"/>
     <tableColumn id="2" xr3:uid="{C1A9F316-18D3-4A60-995E-0510E1E38994}" name="any" dataDxfId="10"/>
@@ -588,7 +597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D38847F-D3AB-4048-9CC8-9BB16BDA546D}">
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -598,7 +607,7 @@
     <col min="11" max="13" width="12.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -636,7 +645,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -675,8 +684,9 @@
         <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
         <v>216.34583333333333</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N2" s="5"/>
+    </row>
+    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -715,8 +725,9 @@
         <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
         <v>165.2891904761905</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N3" s="5"/>
+    </row>
+    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -756,8 +767,9 @@
         <v>188.75084848484849</v>
       </c>
       <c r="M4" s="5"/>
-    </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N4" s="5"/>
+    </row>
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -765,7 +777,7 @@
         <v>2026</v>
       </c>
       <c r="C5" s="2">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>4</v>
@@ -787,17 +799,18 @@
       </c>
       <c r="J5" s="6">
         <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
-        <v>393.44400000000002</v>
+        <v>322.49508196721314</v>
       </c>
       <c r="K5" s="6">
         <v>18562</v>
       </c>
       <c r="L5" s="6">
         <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
-        <v>371.24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304.29508196721309</v>
+      </c>
+      <c r="N5" s="5"/>
+    </row>
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -836,8 +849,9 @@
         <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
         <v>201.19140350877194</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N6" s="5"/>
+    </row>
+    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -876,8 +890,9 @@
         <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
         <v>185.38312500000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N7" s="5"/>
+    </row>
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -885,7 +900,7 @@
         <v>2026</v>
       </c>
       <c r="C8" s="4">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>4</v>
@@ -907,17 +922,18 @@
       </c>
       <c r="J8" s="6">
         <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
-        <v>114.21874015748033</v>
+        <v>149.54412371134021</v>
       </c>
       <c r="K8" s="6">
         <v>14505.78</v>
       </c>
       <c r="L8" s="6">
         <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
-        <v>114.21874015748033</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>149.54412371134021</v>
+      </c>
+      <c r="N8" s="5"/>
+    </row>
+    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -956,8 +972,9 @@
         <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
         <v>117.69003703703704</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N9" s="5"/>
+    </row>
+    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -996,8 +1013,9 @@
         <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
         <v>157.34609442060085</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N10" s="5"/>
+    </row>
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -1036,8 +1054,9 @@
         <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
         <v>218.23406593406594</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N11" s="5"/>
+    </row>
+    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -1076,8 +1095,9 @@
         <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
         <v>133.62672897196262</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N12" s="5"/>
+    </row>
+    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -1117,8 +1137,9 @@
         <v>183.5707142857143</v>
       </c>
       <c r="M13" s="5"/>
-    </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N13" s="5"/>
+    </row>
+    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -1126,7 +1147,7 @@
         <v>2026</v>
       </c>
       <c r="C14" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>4</v>
@@ -1148,17 +1169,18 @@
       </c>
       <c r="J14" s="6">
         <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
-        <v>351.53609374999996</v>
+        <v>349.35263975155277</v>
       </c>
       <c r="K14" s="6">
         <v>53195.78</v>
       </c>
       <c r="L14" s="6">
         <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
-        <v>332.47362499999997</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>330.40857142857141</v>
+      </c>
+      <c r="N14" s="5"/>
+    </row>
+    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -1166,7 +1188,7 @@
         <v>2026</v>
       </c>
       <c r="C15" s="2">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>4</v>
@@ -1188,17 +1210,18 @@
       </c>
       <c r="J15" s="6">
         <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
-        <v>429.61811764705885</v>
+        <v>365.17540000000002</v>
       </c>
       <c r="K15" s="6">
         <v>33577.54</v>
       </c>
       <c r="L15" s="6">
         <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
-        <v>395.02988235294117</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>335.77539999999999</v>
+      </c>
+      <c r="N15" s="5"/>
+    </row>
+    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -1238,8 +1261,9 @@
         <v>241.7361956521739</v>
       </c>
       <c r="M16" s="5"/>
-    </row>
-    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N16" s="5"/>
+    </row>
+    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1278,8 +1302,9 @@
         <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
         <v>253.3218243243243</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N17" s="5"/>
+    </row>
+    <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1318,8 +1343,9 @@
         <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
         <v>204.17372093023255</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="N18" s="5"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -1358,16 +1384,128 @@
         <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
         <v>171.68366666666665</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
+      <c r="N19" s="5"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C20" s="2">
+        <v>177</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="3">
+        <v>48970.74</v>
+      </c>
+      <c r="J20" s="6">
+        <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
+        <v>276.67084745762713</v>
+      </c>
+      <c r="K20" s="3">
+        <v>43248.74</v>
+      </c>
+      <c r="L20" s="6">
+        <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>244.34316384180789</v>
+      </c>
+      <c r="N20" s="5"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C21" s="2">
+        <v>38</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="3">
+        <v>10797.78</v>
+      </c>
+      <c r="J21" s="6">
+        <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
+        <v>284.15210526315792</v>
+      </c>
+      <c r="K21" s="2">
+        <v>9197.7800000000007</v>
+      </c>
+      <c r="L21" s="6">
+        <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>242.04684210526318</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C22" s="2">
+        <v>33</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22" s="3">
+        <v>14668.88</v>
+      </c>
+      <c r="J22" s="6">
+        <f>Tabla1[[#This Row],[p.t.]]/Tabla1[[#This Row],[m²]]</f>
+        <v>444.51151515151514</v>
+      </c>
+      <c r="K22" s="2">
+        <v>13068.88</v>
+      </c>
+      <c r="L22" s="6">
+        <f>Tabla1[[#This Row],[p.net]]/Tabla1[[#This Row],[m²]]</f>
+        <v>396.02666666666664</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
